--- a/artfynd/A 4339-2025 artfynd.xlsx
+++ b/artfynd/A 4339-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122106696</v>
+        <v>122106694</v>
       </c>
       <c r="B2" t="n">
         <v>97129</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>400245</v>
+        <v>400202</v>
       </c>
       <c r="R2" t="n">
-        <v>6436074</v>
+        <v>6436087</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Några dm2</t>
+          <t>Några dm</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122106699</v>
+        <v>122106700</v>
       </c>
       <c r="B3" t="n">
         <v>97129</v>
@@ -815,17 +815,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Höverö, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>400223</v>
+        <v>400203</v>
       </c>
       <c r="R3" t="n">
-        <v>6436150</v>
+        <v>6436145</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Frisk, fertil.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122106693</v>
+        <v>122106690</v>
       </c>
       <c r="B4" t="n">
         <v>97129</v>
@@ -929,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>400243</v>
+        <v>400277</v>
       </c>
       <c r="R4" t="n">
-        <v>6436046</v>
+        <v>6436000</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122106698</v>
+        <v>122106693</v>
       </c>
       <c r="B5" t="n">
         <v>97129</v>
@@ -1036,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>400227</v>
+        <v>400243</v>
       </c>
       <c r="R5" t="n">
-        <v>6436143</v>
+        <v>6436046</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1085,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122106691</v>
+        <v>122106695</v>
       </c>
       <c r="B6" t="n">
         <v>97129</v>
@@ -1143,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>400234</v>
+        <v>400245</v>
       </c>
       <c r="R6" t="n">
-        <v>6436020</v>
+        <v>6436074</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1192,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Många m2</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122106694</v>
+        <v>122106698</v>
       </c>
       <c r="B7" t="n">
         <v>97129</v>
@@ -1250,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>400202</v>
+        <v>400227</v>
       </c>
       <c r="R7" t="n">
-        <v>6436087</v>
+        <v>6436143</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Några dm</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,7 +1433,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122106690</v>
+        <v>122106691</v>
       </c>
       <c r="B9" t="n">
         <v>97129</v>
@@ -1464,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>400277</v>
+        <v>400234</v>
       </c>
       <c r="R9" t="n">
-        <v>6436000</v>
+        <v>6436020</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1513,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Många m2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1540,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122106700</v>
+        <v>122106699</v>
       </c>
       <c r="B10" t="n">
         <v>97129</v>
@@ -1564,26 +1573,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Höverö, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>400203</v>
+        <v>400223</v>
       </c>
       <c r="R10" t="n">
-        <v>6436145</v>
+        <v>6436150</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Frisk, fertil.</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4339-2025 artfynd.xlsx
+++ b/artfynd/A 4339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122106694</v>
+        <v>122106696</v>
       </c>
       <c r="B2" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>400202</v>
+        <v>400245</v>
       </c>
       <c r="R2" t="n">
-        <v>6436087</v>
+        <v>6436074</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Några dm</t>
+          <t>Några dm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122106700</v>
+        <v>122106692</v>
       </c>
       <c r="B3" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,26 +815,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Höverö, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>400203</v>
+        <v>400253</v>
       </c>
       <c r="R3" t="n">
-        <v>6436145</v>
+        <v>6436022</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Frisk, fertil.</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122106690</v>
+        <v>122106700</v>
       </c>
       <c r="B4" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,17 +922,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Höverö, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>400277</v>
+        <v>400203</v>
       </c>
       <c r="R4" t="n">
-        <v>6436000</v>
+        <v>6436145</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Frisk, fertil.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122106693</v>
+        <v>122106691</v>
       </c>
       <c r="B5" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>400243</v>
+        <v>400234</v>
       </c>
       <c r="R5" t="n">
-        <v>6436046</v>
+        <v>6436020</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Många m2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122106695</v>
+        <v>122106693</v>
       </c>
       <c r="B6" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>400245</v>
+        <v>400243</v>
       </c>
       <c r="R6" t="n">
-        <v>6436074</v>
+        <v>6436046</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122106698</v>
+        <v>122106694</v>
       </c>
       <c r="B7" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>400227</v>
+        <v>400202</v>
       </c>
       <c r="R7" t="n">
-        <v>6436143</v>
+        <v>6436087</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Några dm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122106692</v>
+        <v>122106699</v>
       </c>
       <c r="B8" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>400253</v>
+        <v>400223</v>
       </c>
       <c r="R8" t="n">
-        <v>6436022</v>
+        <v>6436150</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122106691</v>
+        <v>122106698</v>
       </c>
       <c r="B9" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>400234</v>
+        <v>400227</v>
       </c>
       <c r="R9" t="n">
-        <v>6436020</v>
+        <v>6436143</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Många m2</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122106699</v>
+        <v>122106690</v>
       </c>
       <c r="B10" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>400223</v>
+        <v>400277</v>
       </c>
       <c r="R10" t="n">
-        <v>6436150</v>
+        <v>6436000</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4339-2025 artfynd.xlsx
+++ b/artfynd/A 4339-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122106692</v>
+        <v>122106693</v>
       </c>
       <c r="B3" t="n">
         <v>97139</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>400253</v>
+        <v>400243</v>
       </c>
       <c r="R3" t="n">
-        <v>6436022</v>
+        <v>6436046</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1005,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122106691</v>
+        <v>122106690</v>
       </c>
       <c r="B5" t="n">
         <v>97139</v>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>400234</v>
+        <v>400277</v>
       </c>
       <c r="R5" t="n">
-        <v>6436020</v>
+        <v>6436000</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Många m2</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122106693</v>
+        <v>122106699</v>
       </c>
       <c r="B6" t="n">
         <v>97139</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>400243</v>
+        <v>400223</v>
       </c>
       <c r="R6" t="n">
-        <v>6436046</v>
+        <v>6436150</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122106694</v>
+        <v>122106698</v>
       </c>
       <c r="B7" t="n">
         <v>97139</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>400202</v>
+        <v>400227</v>
       </c>
       <c r="R7" t="n">
-        <v>6436087</v>
+        <v>6436143</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Några dm</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122106699</v>
+        <v>122106691</v>
       </c>
       <c r="B8" t="n">
         <v>97139</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>400223</v>
+        <v>400234</v>
       </c>
       <c r="R8" t="n">
-        <v>6436150</v>
+        <v>6436020</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Många m2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,7 +1433,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122106698</v>
+        <v>122106694</v>
       </c>
       <c r="B9" t="n">
         <v>97139</v>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>400227</v>
+        <v>400202</v>
       </c>
       <c r="R9" t="n">
-        <v>6436143</v>
+        <v>6436087</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Några dm</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,7 +1540,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122106690</v>
+        <v>122106692</v>
       </c>
       <c r="B10" t="n">
         <v>97139</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>400277</v>
+        <v>400253</v>
       </c>
       <c r="R10" t="n">
-        <v>6436000</v>
+        <v>6436022</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4339-2025 artfynd.xlsx
+++ b/artfynd/A 4339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122106696</v>
       </c>
       <c r="B2" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122106693</v>
+        <v>122106700</v>
       </c>
       <c r="B3" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,17 +815,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Höverö, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>400243</v>
+        <v>400203</v>
       </c>
       <c r="R3" t="n">
-        <v>6436046</v>
+        <v>6436145</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Frisk, fertil.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122106700</v>
+        <v>122106690</v>
       </c>
       <c r="B4" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,26 +931,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Höverö, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>400203</v>
+        <v>400277</v>
       </c>
       <c r="R4" t="n">
-        <v>6436145</v>
+        <v>6436000</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Frisk, fertil.</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122106690</v>
+        <v>122106698</v>
       </c>
       <c r="B5" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>400277</v>
+        <v>400227</v>
       </c>
       <c r="R5" t="n">
-        <v>6436000</v>
+        <v>6436143</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122106699</v>
+        <v>122106693</v>
       </c>
       <c r="B6" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>400223</v>
+        <v>400243</v>
       </c>
       <c r="R6" t="n">
-        <v>6436150</v>
+        <v>6436046</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122106698</v>
+        <v>122106694</v>
       </c>
       <c r="B7" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>400227</v>
+        <v>400202</v>
       </c>
       <c r="R7" t="n">
-        <v>6436143</v>
+        <v>6436087</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Några dm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,7 +1329,7 @@
         <v>122106691</v>
       </c>
       <c r="B8" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122106694</v>
+        <v>122106699</v>
       </c>
       <c r="B9" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>400202</v>
+        <v>400223</v>
       </c>
       <c r="R9" t="n">
-        <v>6436087</v>
+        <v>6436150</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Några dm</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,7 +1543,7 @@
         <v>122106692</v>
       </c>
       <c r="B10" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 4339-2025 artfynd.xlsx
+++ b/artfynd/A 4339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122106696</v>
+        <v>122106694</v>
       </c>
       <c r="B2" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>400245</v>
+        <v>400202</v>
       </c>
       <c r="R2" t="n">
-        <v>6436074</v>
+        <v>6436087</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Några dm2</t>
+          <t>Några dm</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122106700</v>
+        <v>122106697</v>
       </c>
       <c r="B3" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,26 +815,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Höverö, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>400203</v>
+        <v>400245</v>
       </c>
       <c r="R3" t="n">
-        <v>6436145</v>
+        <v>6436074</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Frisk, fertil.</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122106690</v>
+        <v>122106699</v>
       </c>
       <c r="B4" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>400277</v>
+        <v>400223</v>
       </c>
       <c r="R4" t="n">
-        <v>6436000</v>
+        <v>6436150</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122106698</v>
+        <v>122106700</v>
       </c>
       <c r="B5" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,17 +1029,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Höverö, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>400227</v>
+        <v>400203</v>
       </c>
       <c r="R5" t="n">
-        <v>6436143</v>
+        <v>6436145</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Frisk, fertil.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
         <v>122106693</v>
       </c>
       <c r="B6" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122106694</v>
+        <v>122106698</v>
       </c>
       <c r="B7" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>400202</v>
+        <v>400227</v>
       </c>
       <c r="R7" t="n">
-        <v>6436087</v>
+        <v>6436143</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Några dm</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,7 +1329,7 @@
         <v>122106691</v>
       </c>
       <c r="B8" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122106699</v>
+        <v>122106690</v>
       </c>
       <c r="B9" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>400223</v>
+        <v>400277</v>
       </c>
       <c r="R9" t="n">
-        <v>6436150</v>
+        <v>6436000</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,7 +1543,7 @@
         <v>122106692</v>
       </c>
       <c r="B10" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 4339-2025 artfynd.xlsx
+++ b/artfynd/A 4339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122106694</v>
+        <v>122106693</v>
       </c>
       <c r="B2" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>221945</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>400202</v>
+        <v>400243</v>
       </c>
       <c r="R2" t="n">
-        <v>6436087</v>
+        <v>6436046</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Några dm</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122106697</v>
+        <v>122106692</v>
       </c>
       <c r="B3" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,11 +795,6 @@
       <c r="E3" t="n">
         <v>221945</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>400245</v>
+        <v>400253</v>
       </c>
       <c r="R3" t="n">
-        <v>6436074</v>
+        <v>6436022</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122106699</v>
+        <v>122106696</v>
       </c>
       <c r="B4" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,11 +897,6 @@
       <c r="E4" t="n">
         <v>221945</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>400223</v>
+        <v>400245</v>
       </c>
       <c r="R4" t="n">
-        <v>6436150</v>
+        <v>6436074</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Några dm2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122106700</v>
+        <v>122106694</v>
       </c>
       <c r="B5" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,11 +999,6 @@
       <c r="E5" t="n">
         <v>221945</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -1029,26 +1009,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Höverö, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>400203</v>
+        <v>400202</v>
       </c>
       <c r="R5" t="n">
-        <v>6436145</v>
+        <v>6436087</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Frisk, fertil.</t>
+          <t>Några dm</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122106693</v>
+        <v>122106700</v>
       </c>
       <c r="B6" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,11 +1101,6 @@
       <c r="E6" t="n">
         <v>221945</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -1145,17 +1111,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Höverö, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>400243</v>
+        <v>400203</v>
       </c>
       <c r="R6" t="n">
-        <v>6436046</v>
+        <v>6436145</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1192,7 +1167,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Frisk, fertil.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,7 +1197,7 @@
         <v>122106698</v>
       </c>
       <c r="B7" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,11 +1211,6 @@
       </c>
       <c r="E7" t="n">
         <v>221945</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1329,7 +1299,7 @@
         <v>122106691</v>
       </c>
       <c r="B8" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,11 +1313,6 @@
       </c>
       <c r="E8" t="n">
         <v>221945</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1436,7 +1401,7 @@
         <v>122106690</v>
       </c>
       <c r="B9" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,11 +1415,6 @@
       </c>
       <c r="E9" t="n">
         <v>221945</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1540,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122106692</v>
+        <v>122106699</v>
       </c>
       <c r="B10" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,11 +1518,6 @@
       <c r="E10" t="n">
         <v>221945</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -1580,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>400253</v>
+        <v>400223</v>
       </c>
       <c r="R10" t="n">
-        <v>6436022</v>
+        <v>6436150</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 4339-2025 artfynd.xlsx
+++ b/artfynd/A 4339-2025 artfynd.xlsx
@@ -1398,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122106690</v>
+        <v>122106699</v>
       </c>
       <c r="B9" t="n">
         <v>97165</v>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>400277</v>
+        <v>400223</v>
       </c>
       <c r="R9" t="n">
-        <v>6436000</v>
+        <v>6436150</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122106699</v>
+        <v>122106690</v>
       </c>
       <c r="B10" t="n">
         <v>97165</v>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>400223</v>
+        <v>400277</v>
       </c>
       <c r="R10" t="n">
-        <v>6436150</v>
+        <v>6436000</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4339-2025 artfynd.xlsx
+++ b/artfynd/A 4339-2025 artfynd.xlsx
@@ -1398,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122106699</v>
+        <v>122106690</v>
       </c>
       <c r="B9" t="n">
         <v>97165</v>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>400223</v>
+        <v>400277</v>
       </c>
       <c r="R9" t="n">
-        <v>6436150</v>
+        <v>6436000</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122106690</v>
+        <v>122106699</v>
       </c>
       <c r="B10" t="n">
         <v>97165</v>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>400277</v>
+        <v>400223</v>
       </c>
       <c r="R10" t="n">
-        <v>6436000</v>
+        <v>6436150</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4339-2025 artfynd.xlsx
+++ b/artfynd/A 4339-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122106693</v>
+        <v>122106697</v>
       </c>
       <c r="B2" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>221945</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>400243</v>
+        <v>400245</v>
       </c>
       <c r="R2" t="n">
-        <v>6436046</v>
+        <v>6436074</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122106692</v>
+        <v>122106691</v>
       </c>
       <c r="B3" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,6 +800,11 @@
       <c r="E3" t="n">
         <v>221945</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -812,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>400253</v>
+        <v>400234</v>
       </c>
       <c r="R3" t="n">
-        <v>6436022</v>
+        <v>6436020</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Många m2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122106696</v>
+        <v>122106694</v>
       </c>
       <c r="B4" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,6 +907,11 @@
       <c r="E4" t="n">
         <v>221945</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -914,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>400245</v>
+        <v>400202</v>
       </c>
       <c r="R4" t="n">
-        <v>6436074</v>
+        <v>6436087</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -954,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Några dm2</t>
+          <t>Några dm</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122106694</v>
+        <v>122106699</v>
       </c>
       <c r="B5" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,6 +1014,11 @@
       <c r="E5" t="n">
         <v>221945</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -1016,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>400202</v>
+        <v>400223</v>
       </c>
       <c r="R5" t="n">
-        <v>6436087</v>
+        <v>6436150</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1056,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Några dm</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,7 +1106,7 @@
         <v>122106700</v>
       </c>
       <c r="B6" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,6 +1120,11 @@
       </c>
       <c r="E6" t="n">
         <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1194,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122106698</v>
+        <v>122106690</v>
       </c>
       <c r="B7" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,6 +1237,11 @@
       <c r="E7" t="n">
         <v>221945</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -1229,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>400227</v>
+        <v>400277</v>
       </c>
       <c r="R7" t="n">
-        <v>6436143</v>
+        <v>6436000</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1269,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera m2</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122106691</v>
+        <v>122106693</v>
       </c>
       <c r="B8" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,6 +1344,11 @@
       <c r="E8" t="n">
         <v>221945</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -1331,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>400234</v>
+        <v>400243</v>
       </c>
       <c r="R8" t="n">
-        <v>6436020</v>
+        <v>6436046</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1371,7 +1406,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Många m2</t>
+          <t>Stort område, många m2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122106690</v>
+        <v>122106698</v>
       </c>
       <c r="B9" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,6 +1451,11 @@
       <c r="E9" t="n">
         <v>221945</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -1433,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>400277</v>
+        <v>400227</v>
       </c>
       <c r="R9" t="n">
-        <v>6436000</v>
+        <v>6436143</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1473,7 +1513,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Stort område, många m2</t>
+          <t>Flera m2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122106699</v>
+        <v>122106692</v>
       </c>
       <c r="B10" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,6 +1558,11 @@
       <c r="E10" t="n">
         <v>221945</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -1535,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>400223</v>
+        <v>400253</v>
       </c>
       <c r="R10" t="n">
-        <v>6436150</v>
+        <v>6436022</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
